--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -1,69 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29231"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Fer\Python\Monitor de stocks\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C7FB43C-13A1-44A4-A99E-EBF037EDE2CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
-  <si>
-    <t>symbol</t>
-  </si>
-  <si>
-    <t>price</t>
-  </si>
-  <si>
-    <t>time</t>
-  </si>
-  <si>
-    <t>BINANCE:BTCUSDT</t>
-  </si>
-  <si>
-    <t>BINANCE:ETHUSDT</t>
-  </si>
-  <si>
-    <t>BINANCE:SOLUSDT</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -78,44 +49,94 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="3">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -403,56 +424,107 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="17.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.140625" bestFit="1" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2">
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>price</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>time</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B2" t="n">
         <v>110495</v>
       </c>
-      <c r="C2" s="2">
-        <v>45960.036225370372</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3">
+      <c r="C2" s="2" t="n">
+        <v>45960.03622537037</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
         <v>3916.14</v>
       </c>
-      <c r="C3" s="2">
-        <v>45960.036225370372</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4">
+      <c r="C3" s="2" t="n">
+        <v>45960.03622537037</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
         <v>194.02</v>
       </c>
-      <c r="C4" s="2">
-        <v>45960.036225370372</v>
+      <c r="C4" s="2" t="n">
+        <v>45960.03622537037</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>107885.69</v>
+      </c>
+      <c r="C5" s="2" t="n">
+        <v>45960.91649280115</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3768.65</v>
+      </c>
+      <c r="C6" s="2" t="n">
+        <v>45960.91649280115</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>182.19</v>
+      </c>
+      <c r="C7" s="2" t="n">
+        <v>45960.91649280115</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C7"/>
+  <dimension ref="A1:C10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -498,7 +498,7 @@
         <v>107885.69</v>
       </c>
       <c r="C5" s="2" t="n">
-        <v>45960.91649280115</v>
+        <v>45960.91649280093</v>
       </c>
     </row>
     <row r="6">
@@ -511,7 +511,7 @@
         <v>3768.65</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>45960.91649280115</v>
+        <v>45960.91649280093</v>
       </c>
     </row>
     <row r="7">
@@ -524,7 +524,46 @@
         <v>182.19</v>
       </c>
       <c r="C7" s="2" t="n">
-        <v>45960.91649280115</v>
+        <v>45960.91649280093</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>107697.85</v>
+      </c>
+      <c r="C8" s="2" t="n">
+        <v>45960.93484672721</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>3773.6</v>
+      </c>
+      <c r="C9" s="2" t="n">
+        <v>45960.93484672721</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>182.79</v>
+      </c>
+      <c r="C10" s="2" t="n">
+        <v>45960.93484672721</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C10"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -537,7 +537,7 @@
         <v>107697.85</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>45960.93484672721</v>
+        <v>45960.93484672454</v>
       </c>
     </row>
     <row r="9">
@@ -550,7 +550,7 @@
         <v>3773.6</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>45960.93484672721</v>
+        <v>45960.93484672454</v>
       </c>
     </row>
     <row r="10">
@@ -563,7 +563,46 @@
         <v>182.79</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>45960.93484672721</v>
+        <v>45960.93484672454</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>107639.15</v>
+      </c>
+      <c r="C11" s="2" t="n">
+        <v>45960.94427745417</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3773.43</v>
+      </c>
+      <c r="C12" s="2" t="n">
+        <v>45960.94427745417</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>183.14</v>
+      </c>
+      <c r="C13" s="2" t="n">
+        <v>45960.94427745417</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C13"/>
+  <dimension ref="A1:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -576,7 +576,7 @@
         <v>107639.15</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>45960.94427745417</v>
+        <v>45960.9442774537</v>
       </c>
     </row>
     <row r="12">
@@ -589,7 +589,7 @@
         <v>3773.43</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>45960.94427745417</v>
+        <v>45960.9442774537</v>
       </c>
     </row>
     <row r="13">
@@ -602,7 +602,46 @@
         <v>183.14</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>45960.94427745417</v>
+        <v>45960.9442774537</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>107624.53</v>
+      </c>
+      <c r="C14" s="2" t="n">
+        <v>45960.95087142423</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>3769.5</v>
+      </c>
+      <c r="C15" s="2" t="n">
+        <v>45960.95087142423</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>183.14</v>
+      </c>
+      <c r="C16" s="2" t="n">
+        <v>45960.95087142423</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C16"/>
+  <dimension ref="A1:C19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -615,7 +615,7 @@
         <v>107624.53</v>
       </c>
       <c r="C14" s="2" t="n">
-        <v>45960.95087142423</v>
+        <v>45960.95087142361</v>
       </c>
     </row>
     <row r="15">
@@ -628,7 +628,7 @@
         <v>3769.5</v>
       </c>
       <c r="C15" s="2" t="n">
-        <v>45960.95087142423</v>
+        <v>45960.95087142361</v>
       </c>
     </row>
     <row r="16">
@@ -641,7 +641,46 @@
         <v>183.14</v>
       </c>
       <c r="C16" s="2" t="n">
-        <v>45960.95087142423</v>
+        <v>45960.95087142361</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>107901.2</v>
+      </c>
+      <c r="C17" s="2" t="n">
+        <v>45960.95743995188</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>3781.58</v>
+      </c>
+      <c r="C18" s="2" t="n">
+        <v>45960.95743995188</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>183.57</v>
+      </c>
+      <c r="C19" s="2" t="n">
+        <v>45960.95743995188</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C19"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -654,7 +654,7 @@
         <v>107901.2</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>45960.95743995188</v>
+        <v>45960.9574399537</v>
       </c>
     </row>
     <row r="18">
@@ -667,7 +667,7 @@
         <v>3781.58</v>
       </c>
       <c r="C18" s="2" t="n">
-        <v>45960.95743995188</v>
+        <v>45960.9574399537</v>
       </c>
     </row>
     <row r="19">
@@ -680,7 +680,46 @@
         <v>183.57</v>
       </c>
       <c r="C19" s="2" t="n">
-        <v>45960.95743995188</v>
+        <v>45960.9574399537</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>107674.93</v>
+      </c>
+      <c r="C20" s="2" t="n">
+        <v>45960.9740328273</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>3778.26</v>
+      </c>
+      <c r="C21" s="2" t="n">
+        <v>45960.9740328273</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>183.28</v>
+      </c>
+      <c r="C22" s="2" t="n">
+        <v>45960.9740328273</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -693,7 +693,7 @@
         <v>107674.93</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>45960.9740328273</v>
+        <v>45960.97403282407</v>
       </c>
     </row>
     <row r="21">
@@ -706,7 +706,7 @@
         <v>3778.26</v>
       </c>
       <c r="C21" s="2" t="n">
-        <v>45960.9740328273</v>
+        <v>45960.97403282407</v>
       </c>
     </row>
     <row r="22">
@@ -719,7 +719,46 @@
         <v>183.28</v>
       </c>
       <c r="C22" s="2" t="n">
-        <v>45960.9740328273</v>
+        <v>45960.97403282407</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>107842.65</v>
+      </c>
+      <c r="C23" s="2" t="n">
+        <v>45960.98184430617</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>3789.52</v>
+      </c>
+      <c r="C24" s="2" t="n">
+        <v>45960.98184430617</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>184.23</v>
+      </c>
+      <c r="C25" s="2" t="n">
+        <v>45960.98184430617</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C25"/>
+  <dimension ref="A1:C28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -732,7 +732,7 @@
         <v>107842.65</v>
       </c>
       <c r="C23" s="2" t="n">
-        <v>45960.98184430617</v>
+        <v>45960.98184430556</v>
       </c>
     </row>
     <row r="24">
@@ -745,7 +745,7 @@
         <v>3789.52</v>
       </c>
       <c r="C24" s="2" t="n">
-        <v>45960.98184430617</v>
+        <v>45960.98184430556</v>
       </c>
     </row>
     <row r="25">
@@ -758,7 +758,46 @@
         <v>184.23</v>
       </c>
       <c r="C25" s="2" t="n">
-        <v>45960.98184430617</v>
+        <v>45960.98184430556</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>107965.35</v>
+      </c>
+      <c r="C26" s="2" t="n">
+        <v>45960.98850778597</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3785.63</v>
+      </c>
+      <c r="C27" s="2" t="n">
+        <v>45960.98850778597</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>183.49</v>
+      </c>
+      <c r="C28" s="2" t="n">
+        <v>45960.98850778597</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C28"/>
+  <dimension ref="A1:C31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -771,7 +771,7 @@
         <v>107965.35</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>45960.98850778597</v>
+        <v>45960.98850778935</v>
       </c>
     </row>
     <row r="27">
@@ -784,7 +784,7 @@
         <v>3785.63</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>45960.98850778597</v>
+        <v>45960.98850778935</v>
       </c>
     </row>
     <row r="28">
@@ -797,7 +797,46 @@
         <v>183.49</v>
       </c>
       <c r="C28" s="2" t="n">
-        <v>45960.98850778597</v>
+        <v>45960.98850778935</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>108220.32</v>
+      </c>
+      <c r="C29" s="2" t="n">
+        <v>45960.99508392916</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>3798.77</v>
+      </c>
+      <c r="C30" s="2" t="n">
+        <v>45960.99508392916</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>184.38</v>
+      </c>
+      <c r="C31" s="2" t="n">
+        <v>45960.99508392916</v>
       </c>
     </row>
   </sheetData>

--- a/precios_cripto_2.xlsx
+++ b/precios_cripto_2.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C31"/>
+  <dimension ref="A1:C34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -810,7 +810,7 @@
         <v>108220.32</v>
       </c>
       <c r="C29" s="2" t="n">
-        <v>45960.99508392916</v>
+        <v>45960.99508392361</v>
       </c>
     </row>
     <row r="30">
@@ -823,7 +823,7 @@
         <v>3798.77</v>
       </c>
       <c r="C30" s="2" t="n">
-        <v>45960.99508392916</v>
+        <v>45960.99508392361</v>
       </c>
     </row>
     <row r="31">
@@ -836,7 +836,46 @@
         <v>184.38</v>
       </c>
       <c r="C31" s="2" t="n">
-        <v>45960.99508392916</v>
+        <v>45960.99508392361</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>BINANCE:BTCUSDT</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>109330</v>
+      </c>
+      <c r="C32" s="2" t="n">
+        <v>45961.038997933</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>BINANCE:ETHUSDT</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>3832.65</v>
+      </c>
+      <c r="C33" s="2" t="n">
+        <v>45961.038997933</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>BINANCE:SOLUSDT</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>185.68</v>
+      </c>
+      <c r="C34" s="2" t="n">
+        <v>45961.038997933</v>
       </c>
     </row>
   </sheetData>
